--- a/diseases/d054/2000-2004.xlsx
+++ b/diseases/d054/2000-2004.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2546,7 +2546,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -3317,7 +3317,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -4088,7 +4088,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5630,7 +5630,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7172,7 +7172,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7943,7 +7943,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9485,7 +9485,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11027,7 +11027,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11798,7 +11798,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12569,7 +12569,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13340,7 +13340,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14111,7 +14111,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14882,7 +14882,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15653,7 +15653,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16424,7 +16424,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17195,7 +17195,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -17966,7 +17966,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -18737,7 +18737,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -19508,7 +19508,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -20279,7 +20279,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21050,7 +21050,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -21821,7 +21821,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -22592,7 +22592,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -23363,7 +23363,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -24134,7 +24134,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -24905,7 +24905,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -25676,7 +25676,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -26447,7 +26447,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -27218,7 +27218,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -27989,7 +27989,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -28760,7 +28760,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -29531,7 +29531,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -30302,7 +30302,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
@@ -31073,7 +31073,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -31844,7 +31844,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -32615,7 +32615,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -33386,7 +33386,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -34157,7 +34157,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -34928,7 +34928,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
@@ -35699,7 +35699,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -36470,7 +36470,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -37241,7 +37241,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK191" t="inlineStr">
@@ -38012,7 +38012,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -38783,7 +38783,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -39554,7 +39554,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK203" t="inlineStr">
@@ -40325,7 +40325,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
@@ -41096,7 +41096,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
@@ -41867,7 +41867,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK215" t="inlineStr">
@@ -42638,7 +42638,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -43409,7 +43409,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
@@ -44180,7 +44180,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK227" t="inlineStr">
@@ -44951,7 +44951,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
@@ -45722,7 +45722,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK235" t="inlineStr">
@@ -46493,7 +46493,7 @@
       </c>
       <c r="AJ239" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK239" t="inlineStr">

--- a/diseases/d054/2000-2004.xlsx
+++ b/diseases/d054/2000-2004.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2546,7 +2546,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -3317,7 +3317,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -4088,7 +4088,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5630,7 +5630,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7172,7 +7172,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7943,7 +7943,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9485,7 +9485,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11027,7 +11027,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11798,7 +11798,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12569,7 +12569,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13340,7 +13340,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14111,7 +14111,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14882,7 +14882,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15653,7 +15653,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16424,7 +16424,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17195,7 +17195,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -17966,7 +17966,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -18737,7 +18737,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -19508,7 +19508,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -20279,7 +20279,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21050,7 +21050,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -21821,7 +21821,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -22592,7 +22592,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -23363,7 +23363,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -24134,7 +24134,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -24905,7 +24905,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -25676,7 +25676,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -26447,7 +26447,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -27218,7 +27218,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -27989,7 +27989,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -28760,7 +28760,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -29531,7 +29531,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -30302,7 +30302,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
@@ -31073,7 +31073,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -31844,7 +31844,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -32615,7 +32615,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -33386,7 +33386,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -34157,7 +34157,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -34928,7 +34928,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
@@ -35699,7 +35699,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -36470,7 +36470,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -37241,7 +37241,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK191" t="inlineStr">
@@ -38012,7 +38012,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -38783,7 +38783,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -39554,7 +39554,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK203" t="inlineStr">
@@ -40325,7 +40325,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
@@ -41096,7 +41096,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
@@ -41867,7 +41867,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK215" t="inlineStr">
@@ -42638,7 +42638,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -43409,7 +43409,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
@@ -44180,7 +44180,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK227" t="inlineStr">
@@ -44951,7 +44951,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
@@ -45722,7 +45722,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK235" t="inlineStr">
@@ -46493,7 +46493,7 @@
       </c>
       <c r="AJ239" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK239" t="inlineStr">

--- a/diseases/d054/2000-2004.xlsx
+++ b/diseases/d054/2000-2004.xlsx
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN3" t="b">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN7" t="b">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN11" t="b">
@@ -3327,7 +3327,7 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN15" t="b">
@@ -4098,7 +4098,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN19" t="b">
@@ -4869,7 +4869,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN23" t="b">
@@ -5640,7 +5640,7 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN27" t="b">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN31" t="b">
@@ -7182,7 +7182,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN35" t="b">
@@ -7953,7 +7953,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN39" t="b">
@@ -8724,7 +8724,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN43" t="b">
@@ -9495,7 +9495,7 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN47" t="b">
@@ -10266,7 +10266,7 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN51" t="b">
@@ -11037,7 +11037,7 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN55" t="b">
@@ -11808,7 +11808,7 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN59" t="b">
@@ -12579,7 +12579,7 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN63" t="b">
@@ -13350,7 +13350,7 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN67" t="b">
@@ -14121,7 +14121,7 @@
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN71" t="b">
@@ -14892,7 +14892,7 @@
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN75" t="b">
@@ -15663,7 +15663,7 @@
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN79" t="b">
@@ -16434,7 +16434,7 @@
       </c>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN83" t="b">
@@ -17205,7 +17205,7 @@
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN87" t="b">
@@ -17976,7 +17976,7 @@
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN91" t="b">
@@ -18747,7 +18747,7 @@
       </c>
       <c r="AM95" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN95" t="b">
@@ -19518,7 +19518,7 @@
       </c>
       <c r="AM99" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN99" t="b">
@@ -20289,7 +20289,7 @@
       </c>
       <c r="AM103" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN103" t="b">
@@ -21060,7 +21060,7 @@
       </c>
       <c r="AM107" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN107" t="b">
@@ -21831,7 +21831,7 @@
       </c>
       <c r="AM111" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN111" t="b">
@@ -22602,7 +22602,7 @@
       </c>
       <c r="AM115" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN115" t="b">
@@ -23373,7 +23373,7 @@
       </c>
       <c r="AM119" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN119" t="b">
@@ -24144,7 +24144,7 @@
       </c>
       <c r="AM123" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN123" t="b">
@@ -24915,7 +24915,7 @@
       </c>
       <c r="AM127" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN127" t="b">
@@ -25686,7 +25686,7 @@
       </c>
       <c r="AM131" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN131" t="b">
@@ -26457,7 +26457,7 @@
       </c>
       <c r="AM135" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN135" t="b">
@@ -27228,7 +27228,7 @@
       </c>
       <c r="AM139" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN139" t="b">
@@ -27999,7 +27999,7 @@
       </c>
       <c r="AM143" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN143" t="b">
@@ -28770,7 +28770,7 @@
       </c>
       <c r="AM147" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN147" t="b">
@@ -29541,7 +29541,7 @@
       </c>
       <c r="AM151" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN151" t="b">
@@ -30312,7 +30312,7 @@
       </c>
       <c r="AM155" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN155" t="b">
@@ -31083,7 +31083,7 @@
       </c>
       <c r="AM159" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN159" t="b">
@@ -31854,7 +31854,7 @@
       </c>
       <c r="AM163" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN163" t="b">
@@ -32625,7 +32625,7 @@
       </c>
       <c r="AM167" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN167" t="b">
@@ -33396,7 +33396,7 @@
       </c>
       <c r="AM171" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN171" t="b">
@@ -34167,7 +34167,7 @@
       </c>
       <c r="AM175" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN175" t="b">
@@ -34938,7 +34938,7 @@
       </c>
       <c r="AM179" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN179" t="b">
@@ -35709,7 +35709,7 @@
       </c>
       <c r="AM183" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN183" t="b">
@@ -36480,7 +36480,7 @@
       </c>
       <c r="AM187" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN187" t="b">
@@ -37251,7 +37251,7 @@
       </c>
       <c r="AM191" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN191" t="b">
@@ -38022,7 +38022,7 @@
       </c>
       <c r="AM195" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN195" t="b">
@@ -38793,7 +38793,7 @@
       </c>
       <c r="AM199" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN199" t="b">
@@ -39564,7 +39564,7 @@
       </c>
       <c r="AM203" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN203" t="b">
@@ -40335,7 +40335,7 @@
       </c>
       <c r="AM207" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN207" t="b">
@@ -41106,7 +41106,7 @@
       </c>
       <c r="AM211" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN211" t="b">
@@ -41877,7 +41877,7 @@
       </c>
       <c r="AM215" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN215" t="b">
@@ -42648,7 +42648,7 @@
       </c>
       <c r="AM219" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN219" t="b">
@@ -43419,7 +43419,7 @@
       </c>
       <c r="AM223" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN223" t="b">
@@ -44190,7 +44190,7 @@
       </c>
       <c r="AM227" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN227" t="b">
@@ -44961,7 +44961,7 @@
       </c>
       <c r="AM231" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN231" t="b">
@@ -45732,7 +45732,7 @@
       </c>
       <c r="AM235" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN235" t="b">
@@ -46503,7 +46503,7 @@
       </c>
       <c r="AM239" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN239" t="b">

--- a/diseases/d054/2000-2004.xlsx
+++ b/diseases/d054/2000-2004.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2546,7 +2546,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -3317,7 +3317,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -4088,7 +4088,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5630,7 +5630,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7172,7 +7172,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7943,7 +7943,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9485,7 +9485,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11027,7 +11027,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11798,7 +11798,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12569,7 +12569,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13340,7 +13340,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14111,7 +14111,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14882,7 +14882,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15653,7 +15653,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16424,7 +16424,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17195,7 +17195,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -17966,7 +17966,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -18737,7 +18737,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -19508,7 +19508,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -20279,7 +20279,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21050,7 +21050,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -21821,7 +21821,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -22592,7 +22592,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -23363,7 +23363,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -24134,7 +24134,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -24905,7 +24905,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -25676,7 +25676,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -26447,7 +26447,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -27218,7 +27218,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -27989,7 +27989,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -28760,7 +28760,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -29531,7 +29531,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -30302,7 +30302,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
@@ -31073,7 +31073,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -31844,7 +31844,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -32615,7 +32615,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -33386,7 +33386,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -34157,7 +34157,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -34928,7 +34928,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
@@ -35699,7 +35699,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -36470,7 +36470,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -37241,7 +37241,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK191" t="inlineStr">
@@ -38012,7 +38012,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -38783,7 +38783,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -39554,7 +39554,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK203" t="inlineStr">
@@ -40325,7 +40325,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
@@ -41096,7 +41096,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
@@ -41867,7 +41867,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK215" t="inlineStr">
@@ -42638,7 +42638,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -43409,7 +43409,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
@@ -44180,7 +44180,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK227" t="inlineStr">
@@ -44951,7 +44951,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
@@ -45722,7 +45722,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK235" t="inlineStr">
@@ -46493,7 +46493,7 @@
       </c>
       <c r="AJ239" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK239" t="inlineStr">

--- a/diseases/d054/2000-2004.xlsx
+++ b/diseases/d054/2000-2004.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2546,7 +2546,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -3317,7 +3317,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -4088,7 +4088,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5630,7 +5630,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7172,7 +7172,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7943,7 +7943,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9485,7 +9485,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11027,7 +11027,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11798,7 +11798,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12569,7 +12569,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13340,7 +13340,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14111,7 +14111,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14882,7 +14882,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15653,7 +15653,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16424,7 +16424,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17195,7 +17195,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -17966,7 +17966,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -18737,7 +18737,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -19508,7 +19508,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -20279,7 +20279,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21050,7 +21050,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -21821,7 +21821,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -22592,7 +22592,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -23363,7 +23363,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -24134,7 +24134,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -24905,7 +24905,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -25676,7 +25676,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -26447,7 +26447,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -27218,7 +27218,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -27989,7 +27989,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -28760,7 +28760,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -29531,7 +29531,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -30302,7 +30302,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
@@ -31073,7 +31073,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -31844,7 +31844,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -32615,7 +32615,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -33386,7 +33386,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -34157,7 +34157,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -34928,7 +34928,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
@@ -35699,7 +35699,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -36470,7 +36470,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -37241,7 +37241,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK191" t="inlineStr">
@@ -38012,7 +38012,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -38783,7 +38783,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -39554,7 +39554,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK203" t="inlineStr">
@@ -40325,7 +40325,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
@@ -41096,7 +41096,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
@@ -41867,7 +41867,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK215" t="inlineStr">
@@ -42638,7 +42638,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -43409,7 +43409,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
@@ -44180,7 +44180,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK227" t="inlineStr">
@@ -44951,7 +44951,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
@@ -45722,7 +45722,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK235" t="inlineStr">
@@ -46493,7 +46493,7 @@
       </c>
       <c r="AJ239" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK239" t="inlineStr">

--- a/diseases/d054/2000-2004.xlsx
+++ b/diseases/d054/2000-2004.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2546,7 +2546,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -3317,7 +3317,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -4088,7 +4088,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5630,7 +5630,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7172,7 +7172,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7943,7 +7943,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9485,7 +9485,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11027,7 +11027,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11798,7 +11798,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12569,7 +12569,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13340,7 +13340,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14111,7 +14111,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14882,7 +14882,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15653,7 +15653,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16424,7 +16424,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17195,7 +17195,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -17966,7 +17966,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -18737,7 +18737,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -19508,7 +19508,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -20279,7 +20279,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21050,7 +21050,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -21821,7 +21821,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -22592,7 +22592,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -23363,7 +23363,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -24134,7 +24134,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -24905,7 +24905,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -25676,7 +25676,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -26447,7 +26447,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -27218,7 +27218,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -27989,7 +27989,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -28760,7 +28760,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -29531,7 +29531,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -30302,7 +30302,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
@@ -31073,7 +31073,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -31844,7 +31844,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -32615,7 +32615,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -33386,7 +33386,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -34157,7 +34157,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -34928,7 +34928,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
@@ -35699,7 +35699,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -36470,7 +36470,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -37241,7 +37241,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK191" t="inlineStr">
@@ -38012,7 +38012,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -38783,7 +38783,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -39554,7 +39554,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK203" t="inlineStr">
@@ -40325,7 +40325,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
@@ -41096,7 +41096,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
@@ -41867,7 +41867,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK215" t="inlineStr">
@@ -42638,7 +42638,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -43409,7 +43409,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
@@ -44180,7 +44180,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK227" t="inlineStr">
@@ -44951,7 +44951,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
@@ -45722,7 +45722,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK235" t="inlineStr">
@@ -46493,7 +46493,7 @@
       </c>
       <c r="AJ239" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK239" t="inlineStr">
